--- a/pages/TEMPLATE METAR.xlsx
+++ b/pages/TEMPLATE METAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zavie\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9853B2C7-1BC5-4416-A9FA-22DE6685FF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CA849F-8011-48D8-9601-9AE49E8DD604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="[$-421]dd\ mmmm\ yyyy"/>
+    <numFmt numFmtId="164" formatCode="[$-421]dd\ mmmm\ yyyy"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -365,38 +365,38 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,7 +767,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="9.85546875" style="1" customWidth="1"/>
@@ -780,65 +780,65 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="15">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+    </row>
+    <row r="2" spans="1:10" ht="15">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="16" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+    </row>
+    <row r="3" spans="1:10" ht="15">
+      <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+    </row>
+    <row r="4" spans="1:10" ht="15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18">
+      <c r="E4" s="25"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="26">
         <v>46023</v>
       </c>
-      <c r="H4" s="18"/>
+      <c r="H4" s="26"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -850,51 +850,51 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:10" ht="15">
+      <c r="A6" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="20"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="26"/>
-    </row>
-    <row r="8" spans="1:10">
+    <row r="7" spans="1:10" ht="15">
+      <c r="A7" s="23"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="21"/>
+    </row>
+    <row r="8" spans="1:10" ht="24" customHeight="1">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -906,7 +906,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="13"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="24" customHeight="1">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -918,7 +918,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="13"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="24" customHeight="1">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -930,7 +930,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="13"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" ht="24" customHeight="1">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -942,7 +942,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="13"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="24" customHeight="1">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -954,7 +954,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="13"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="24" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -966,7 +966,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="13"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="24" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -978,7 +978,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" ht="24" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -990,7 +990,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="13"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" ht="24" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1002,7 +1002,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="13"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" ht="24" customHeight="1">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1014,7 +1014,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="13"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" ht="24" customHeight="1">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1026,7 +1026,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" ht="24" customHeight="1">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1038,7 +1038,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" ht="24" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1050,7 +1050,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" ht="24" customHeight="1">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1062,7 +1062,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="13"/>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" ht="24" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1074,7 +1074,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="13"/>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" ht="24" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1086,7 +1086,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="13"/>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" ht="24" customHeight="1">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1098,7 +1098,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="13"/>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" ht="24" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1110,7 +1110,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="13"/>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" ht="24" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1122,7 +1122,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="13"/>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" ht="24" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1134,7 +1134,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="13"/>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" ht="24" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1146,7 +1146,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" ht="24" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1158,7 +1158,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="13"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" ht="24" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1170,7 +1170,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="13"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" ht="24" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -1184,21 +1184,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
     <mergeCell ref="J6:J7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/pages/TEMPLATE METAR.xlsx
+++ b/pages/TEMPLATE METAR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zavie\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CA849F-8011-48D8-9601-9AE49E8DD604}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB74B65A-A3C4-476F-A255-9DA5FD67886B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,30 +365,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -397,6 +373,30 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -767,7 +767,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="9.85546875" style="1" customWidth="1"/>
@@ -780,65 +780,65 @@
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-    </row>
-    <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-    </row>
-    <row r="3" spans="1:10" ht="15">
-      <c r="A3" s="24" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-    </row>
-    <row r="4" spans="1:10" ht="15">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="26">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="18">
         <v>46023</v>
       </c>
-      <c r="H4" s="26"/>
+      <c r="H4" s="18"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="15">
+    <row r="5" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -850,51 +850,51 @@
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="15">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:10">
+      <c r="A6" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="25" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15">
-      <c r="A7" s="23"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="21"/>
-    </row>
-    <row r="8" spans="1:10" ht="24" customHeight="1">
+    <row r="7" spans="1:10">
+      <c r="A7" s="20"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="26"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -906,7 +906,7 @@
       <c r="I8" s="12"/>
       <c r="J8" s="13"/>
     </row>
-    <row r="9" spans="1:10" ht="24" customHeight="1">
+    <row r="9" spans="1:10">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -918,7 +918,7 @@
       <c r="I9" s="12"/>
       <c r="J9" s="13"/>
     </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1">
+    <row r="10" spans="1:10">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -930,7 +930,7 @@
       <c r="I10" s="12"/>
       <c r="J10" s="13"/>
     </row>
-    <row r="11" spans="1:10" ht="24" customHeight="1">
+    <row r="11" spans="1:10">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -942,7 +942,7 @@
       <c r="I11" s="12"/>
       <c r="J11" s="13"/>
     </row>
-    <row r="12" spans="1:10" ht="24" customHeight="1">
+    <row r="12" spans="1:10">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -954,7 +954,7 @@
       <c r="I12" s="12"/>
       <c r="J12" s="13"/>
     </row>
-    <row r="13" spans="1:10" ht="24" customHeight="1">
+    <row r="13" spans="1:10">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -966,7 +966,7 @@
       <c r="I13" s="12"/>
       <c r="J13" s="13"/>
     </row>
-    <row r="14" spans="1:10" ht="24" customHeight="1">
+    <row r="14" spans="1:10">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -978,7 +978,7 @@
       <c r="I14" s="12"/>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:10" ht="24" customHeight="1">
+    <row r="15" spans="1:10">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -990,7 +990,7 @@
       <c r="I15" s="12"/>
       <c r="J15" s="13"/>
     </row>
-    <row r="16" spans="1:10" ht="24" customHeight="1">
+    <row r="16" spans="1:10">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1002,7 +1002,7 @@
       <c r="I16" s="12"/>
       <c r="J16" s="13"/>
     </row>
-    <row r="17" spans="1:10" ht="24" customHeight="1">
+    <row r="17" spans="1:10">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1014,7 +1014,7 @@
       <c r="I17" s="12"/>
       <c r="J17" s="13"/>
     </row>
-    <row r="18" spans="1:10" ht="24" customHeight="1">
+    <row r="18" spans="1:10">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1026,7 +1026,7 @@
       <c r="I18" s="12"/>
       <c r="J18" s="13"/>
     </row>
-    <row r="19" spans="1:10" ht="24" customHeight="1">
+    <row r="19" spans="1:10">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1038,7 +1038,7 @@
       <c r="I19" s="12"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="1:10" ht="24" customHeight="1">
+    <row r="20" spans="1:10">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1050,7 +1050,7 @@
       <c r="I20" s="12"/>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="1:10" ht="24" customHeight="1">
+    <row r="21" spans="1:10">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1062,7 +1062,7 @@
       <c r="I21" s="12"/>
       <c r="J21" s="13"/>
     </row>
-    <row r="22" spans="1:10" ht="24" customHeight="1">
+    <row r="22" spans="1:10">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1074,7 +1074,7 @@
       <c r="I22" s="12"/>
       <c r="J22" s="13"/>
     </row>
-    <row r="23" spans="1:10" ht="24" customHeight="1">
+    <row r="23" spans="1:10">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1086,7 +1086,7 @@
       <c r="I23" s="12"/>
       <c r="J23" s="13"/>
     </row>
-    <row r="24" spans="1:10" ht="24" customHeight="1">
+    <row r="24" spans="1:10">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1098,7 +1098,7 @@
       <c r="I24" s="12"/>
       <c r="J24" s="13"/>
     </row>
-    <row r="25" spans="1:10" ht="24" customHeight="1">
+    <row r="25" spans="1:10">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1110,7 +1110,7 @@
       <c r="I25" s="12"/>
       <c r="J25" s="13"/>
     </row>
-    <row r="26" spans="1:10" ht="24" customHeight="1">
+    <row r="26" spans="1:10">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1122,7 +1122,7 @@
       <c r="I26" s="12"/>
       <c r="J26" s="13"/>
     </row>
-    <row r="27" spans="1:10" ht="24" customHeight="1">
+    <row r="27" spans="1:10">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1134,7 +1134,7 @@
       <c r="I27" s="12"/>
       <c r="J27" s="13"/>
     </row>
-    <row r="28" spans="1:10" ht="24" customHeight="1">
+    <row r="28" spans="1:10">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1146,7 +1146,7 @@
       <c r="I28" s="12"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="29" spans="1:10" ht="24" customHeight="1">
+    <row r="29" spans="1:10">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1158,7 +1158,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="13"/>
     </row>
-    <row r="30" spans="1:10" ht="24" customHeight="1">
+    <row r="30" spans="1:10">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1170,7 +1170,7 @@
       <c r="I30" s="12"/>
       <c r="J30" s="13"/>
     </row>
-    <row r="31" spans="1:10" ht="24" customHeight="1">
+    <row r="31" spans="1:10">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -1184,21 +1184,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
